--- a/artfynd/A 51697-2021 artfynd.xlsx
+++ b/artfynd/A 51697-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51697-2021 artfynd.xlsx
+++ b/artfynd/A 51697-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89818876</v>
+        <v>89818805</v>
       </c>
       <c r="B2" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>208242</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601131.7986969555</v>
+        <v>601198</v>
       </c>
       <c r="R2" t="n">
-        <v>6504643.030667382</v>
+        <v>6504469</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,21 +747,11 @@
           <t>2020-06-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-06-11</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>JMN0065 Calluna AB</t>
@@ -780,6 +765,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>15 individer. Lekvatten</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -789,22 +779,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Jonas Mattsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89818805</v>
+        <v>89818876</v>
       </c>
       <c r="B3" t="n">
-        <v>57585</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208242</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601197.8402817376</v>
+        <v>601132</v>
       </c>
       <c r="R3" t="n">
-        <v>6504468.875346724</v>
+        <v>6504643</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -873,21 +858,11 @@
           <t>2020-06-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-06-11</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>JMN0065 Calluna AB</t>
@@ -901,11 +876,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>15 individer. Lekvatten</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -915,10 +885,328 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>89818801</v>
+      </c>
+      <c r="B4" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Oxelösund Hedenlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>601132</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6504469</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tunaberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>JMN0065 Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Jonas Mattsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>89818804</v>
+      </c>
+      <c r="B5" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Oxelösund Hedenlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>601188</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6504474</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tunaberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>JMN0065 Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>89818806</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Oxelösund Hedenlunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>601224</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6504456</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tunaberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>JMN0065 Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51697-2021 artfynd.xlsx
+++ b/artfynd/A 51697-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89818805</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89818876</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89818801</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89818804</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,8 +1232,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89818806</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>